--- a/draft-icl/processes/laser/template.xlsx
+++ b/draft-icl/processes/laser/template.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\greg.steenvoorden\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{34F4EBB0-2804-4F7C-81F8-E060E99A980F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="292" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -2941,7 +2936,7 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
-  <pageSetup paperSize="9" scale="84" fitToWidth="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="84" fitToWidth="0" orientation="landscape"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId2"/>
 </worksheet>
